--- a/supplementary/Table S3.xlsx
+++ b/supplementary/Table S3.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,64 +429,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Gene_A</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Gene_B</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Both_Mutated_n</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Gene_A_Only_n</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Gene_B_Only_n</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Neither_Mutated_n</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Odds_Ratio</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Log2_Odds_Ratio</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>P_Value_Fisher</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gene A</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Gene B</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Both Mutated n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gene A Only n</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Gene B Only n</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Neither Mutated n</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Odds Ratio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Log2 Odds Ratio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P Value Fisher</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Tendency</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>FDR_q_Value</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Statistical_Significance</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FDR q Value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statistical Significance</t>
         </is>
       </c>
     </row>
@@ -562,7 +574,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.001868344465448777</v>
+        <v>0.0018683444654487</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -608,7 +620,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.001868344465448777</v>
+        <v>0.0018683444654487</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -654,7 +666,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.001912326095551382</v>
+        <v>0.0019123260955513</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -700,7 +712,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.002106792384352243</v>
+        <v>0.0021067923843522</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -738,7 +750,7 @@
         <v>1.784</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001726626864896961</v>
+        <v>0.0001726626864896</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -746,7 +758,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.003135407026486184</v>
+        <v>0.0031354070264861</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -784,7 +796,7 @@
         <v>1.375</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001937643709938506</v>
+        <v>0.0001937643709938</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -792,7 +804,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.003135407026486184</v>
+        <v>0.0031354070264861</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -830,7 +842,7 @@
         <v>1.596</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002090271350990789</v>
+        <v>0.000209027135099</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -838,7 +850,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.003135407026486184</v>
+        <v>0.0031354070264861</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -876,7 +888,7 @@
         <v>1.738</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003438979903858561</v>
+        <v>0.0003438979903858</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -884,7 +896,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.004294901839625874</v>
+        <v>0.0042949018396258</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -922,7 +934,7 @@
         <v>1.288</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0003579084866354895</v>
+        <v>0.0003579084866354</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -930,7 +942,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.004294901839625874</v>
+        <v>0.0042949018396258</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -968,7 +980,7 @@
         <v>1.345</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0005816052790444648</v>
+        <v>0.0005816052790444</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -976,7 +988,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.005905373909301945</v>
+        <v>0.0059053739093019</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1014,7 +1026,7 @@
         <v>1.783</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0005905373909301945</v>
+        <v>0.0005905373909301</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1022,7 +1034,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.005905373909301945</v>
+        <v>0.0059053739093019</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1060,7 +1072,7 @@
         <v>0.976</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001052860541805265</v>
+        <v>0.0010528605418052</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1068,7 +1080,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.009718712693587064</v>
+        <v>0.009718712693586999</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1106,7 +1118,7 @@
         <v>1.596</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001155209509377355</v>
+        <v>0.0011552095093773</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1114,7 +1126,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.009901795794663043</v>
+        <v>0.009901795794663</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1152,7 +1164,7 @@
         <v>1.25</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001263106552888558</v>
+        <v>0.0012631065528885</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1160,7 +1172,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.01002558124285925</v>
+        <v>0.0100255812428592</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1198,7 +1210,7 @@
         <v>1.192</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001336744165714567</v>
+        <v>0.0013367441657145</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1206,7 +1218,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.01002558124285925</v>
+        <v>0.0100255812428592</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1244,7 +1256,7 @@
         <v>1.246</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001427703496987247</v>
+        <v>0.0014277034969872</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1252,7 +1264,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.01007790703755704</v>
+        <v>0.010077907037557</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1290,7 +1302,7 @@
         <v>1.005</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00152826569771821</v>
+        <v>0.0015282656977182</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1298,7 +1310,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.01018843798478807</v>
+        <v>0.010188437984788</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1336,7 +1348,7 @@
         <v>1.367</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002297821260231605</v>
+        <v>0.0022978212602316</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1344,7 +1356,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.01451255532777856</v>
+        <v>0.0145125553277785</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1382,7 +1394,7 @@
         <v>1.103</v>
       </c>
       <c r="I21" t="n">
-        <v>0.003102642346216178</v>
+        <v>0.0031026423462161</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1390,7 +1402,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.01829706916156583</v>
+        <v>0.0182970691615658</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1428,7 +1440,7 @@
         <v>0.922</v>
       </c>
       <c r="I22" t="n">
-        <v>0.003348697784263292</v>
+        <v>0.0033486977842632</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1436,7 +1448,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.01829706916156583</v>
+        <v>0.0182970691615658</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1474,7 +1486,7 @@
         <v>0.896</v>
       </c>
       <c r="I23" t="n">
-        <v>0.003354462679620402</v>
+        <v>0.0033544626796204</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1482,7 +1494,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.01829706916156583</v>
+        <v>0.0182970691615658</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1520,7 +1532,7 @@
         <v>1.103</v>
       </c>
       <c r="I24" t="n">
-        <v>0.003571594918896079</v>
+        <v>0.003571594918896</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1528,7 +1540,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.01863440827250128</v>
+        <v>0.0186344082725012</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1566,7 +1578,7 @@
         <v>0.98</v>
       </c>
       <c r="I25" t="n">
-        <v>0.003739607592826469</v>
+        <v>0.0037396075928264</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1574,7 +1586,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.01869803796413234</v>
+        <v>0.0186980379641323</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1612,7 +1624,7 @@
         <v>0.995</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004172591351662119</v>
+        <v>0.0041725913516621</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1620,7 +1632,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.02002843848797817</v>
+        <v>0.0200284384879781</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1658,7 +1670,7 @@
         <v>1.209</v>
       </c>
       <c r="I27" t="n">
-        <v>0.004533673165268195</v>
+        <v>0.0045336731652681</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1666,7 +1678,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.02015365472715513</v>
+        <v>0.0201536547271551</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1704,7 +1716,7 @@
         <v>1.123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.004534572313609903</v>
+        <v>0.0045345723136099</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1712,7 +1724,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.02015365472715513</v>
+        <v>0.0201536547271551</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1750,7 +1762,7 @@
         <v>1.036</v>
       </c>
       <c r="I29" t="n">
-        <v>0.005030124428634874</v>
+        <v>0.0050301244286348</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1758,7 +1770,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.02155767612272089</v>
+        <v>0.0215576761227208</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1796,7 +1808,7 @@
         <v>1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.005575778505543142</v>
+        <v>0.0055757785055431</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1804,7 +1816,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.02307218691948886</v>
+        <v>0.0230721869194888</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1842,7 +1854,7 @@
         <v>0.832</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00600254465751485</v>
+        <v>0.0060025446575148</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1888,7 +1900,7 @@
         <v>0.955</v>
       </c>
       <c r="I32" t="n">
-        <v>0.007891408201843593</v>
+        <v>0.007891408201843499</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1896,7 +1908,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.03054738658778165</v>
+        <v>0.0305473865877816</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1934,7 +1946,7 @@
         <v>1.187</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00906184542094059</v>
+        <v>0.0090618454209405</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1942,7 +1954,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.03398192032852721</v>
+        <v>0.0339819203285272</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1980,7 +1992,7 @@
         <v>0.959</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01355516180267916</v>
+        <v>0.0135551618026791</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1988,7 +2000,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.04891944772766751</v>
+        <v>0.0489194477276675</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2026,7 +2038,7 @@
         <v>1.074</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0138605101895058</v>
+        <v>0.0138605101895057</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2034,7 +2046,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.04891944772766751</v>
+        <v>0.0489194477276675</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2072,7 +2084,7 @@
         <v>0.915</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01673172131941764</v>
+        <v>0.0167317213194176</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2080,7 +2092,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.05736590166657475</v>
+        <v>0.0573659016665747</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2118,7 +2130,7 @@
         <v>1.172</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01939371931025534</v>
+        <v>0.0193937193102553</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2126,7 +2138,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.06464573103418447</v>
+        <v>0.0646457310341844</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2164,7 +2176,7 @@
         <v>0.825</v>
       </c>
       <c r="I38" t="n">
-        <v>0.02117520495869103</v>
+        <v>0.021175204958691</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2172,7 +2184,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.06867634040656549</v>
+        <v>0.06867634040656539</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2210,7 +2222,7 @@
         <v>0.916</v>
       </c>
       <c r="I39" t="n">
-        <v>0.02284511411213328</v>
+        <v>0.0228451141121332</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2218,7 +2230,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.07214246561726301</v>
+        <v>0.07214246561726299</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2256,7 +2268,7 @@
         <v>1.161</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02399293098081184</v>
+        <v>0.0239929309808118</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2264,7 +2276,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.07382440301788258</v>
+        <v>0.0738244030178825</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2302,7 +2314,7 @@
         <v>1.049</v>
       </c>
       <c r="I41" t="n">
-        <v>0.02671003079861209</v>
+        <v>0.026710030798612</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2310,7 +2322,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.08013009239583627</v>
+        <v>0.0801300923958362</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2348,7 +2360,7 @@
         <v>1.069</v>
       </c>
       <c r="I42" t="n">
-        <v>0.02906923775345337</v>
+        <v>0.0290692377534533</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2356,7 +2368,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.08508069586376597</v>
+        <v>0.0850806958637659</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2394,7 +2406,7 @@
         <v>1.017</v>
       </c>
       <c r="I43" t="n">
-        <v>0.03160070795986002</v>
+        <v>0.03160070795986</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2402,7 +2414,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.09016375027261338</v>
+        <v>0.09016375027261329</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2440,7 +2452,7 @@
         <v>1.151</v>
       </c>
       <c r="I44" t="n">
-        <v>0.03230867718101979</v>
+        <v>0.0323086771810197</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2448,7 +2460,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.09016375027261338</v>
+        <v>0.09016375027261329</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2486,7 +2498,7 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0.03501339101890286</v>
+        <v>0.0350133910189028</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2532,7 +2544,7 @@
         <v>0.885</v>
       </c>
       <c r="I46" t="n">
-        <v>0.03978167719035699</v>
+        <v>0.0397816771903569</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2578,7 +2590,7 @@
         <v>0.963</v>
       </c>
       <c r="I47" t="n">
-        <v>0.04617963675088504</v>
+        <v>0.046179636750885</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2586,7 +2598,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.1204686176110045</v>
+        <v>0.1204686176110044</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2624,7 +2636,7 @@
         <v>0.616</v>
       </c>
       <c r="I48" t="n">
-        <v>0.04845775912122985</v>
+        <v>0.0484577591212298</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2670,7 +2682,7 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.05035848371081129</v>
+        <v>0.0503584837108112</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2716,7 +2728,7 @@
         <v>0.653</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05527712195255408</v>
+        <v>0.055277121952554</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2762,7 +2774,7 @@
         <v>0.946</v>
       </c>
       <c r="I51" t="n">
-        <v>0.05712469591124068</v>
+        <v>0.0571246959112406</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2808,7 +2820,7 @@
         <v>0.984</v>
       </c>
       <c r="I52" t="n">
-        <v>0.05989546868094038</v>
+        <v>0.0598954686809403</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2854,7 +2866,7 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>0.05996737272515064</v>
+        <v>0.0599673727251506</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2900,7 +2912,7 @@
         <v>0.59</v>
       </c>
       <c r="I54" t="n">
-        <v>0.07085049528030367</v>
+        <v>0.0708504952803036</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2946,7 +2958,7 @@
         <v>0.741</v>
       </c>
       <c r="I55" t="n">
-        <v>0.08355523042462405</v>
+        <v>0.083555230424624</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2992,7 +3004,7 @@
         <v>0.662</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08556869137683738</v>
+        <v>0.0855686913768373</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3084,7 +3096,7 @@
         <v>0.695</v>
       </c>
       <c r="I58" t="n">
-        <v>0.08771500970140772</v>
+        <v>0.08771500970140771</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3130,7 +3142,7 @@
         <v>0.796</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08821001202544612</v>
+        <v>0.08821001202544609</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3176,7 +3188,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>0.09430198777050147</v>
+        <v>0.0943019877705014</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3222,7 +3234,7 @@
         <v>0.822</v>
       </c>
       <c r="I61" t="n">
-        <v>0.09858878565122328</v>
+        <v>0.0985887856512232</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3230,7 +3242,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.1971775713024466</v>
+        <v>0.1971775713024465</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3406,7 +3418,7 @@
         <v>0.533</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1423254556440677</v>
+        <v>0.1423254556440676</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3460,7 +3472,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.2729245413005078</v>
+        <v>0.2729245413005077</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3498,7 +3510,7 @@
         <v>0.534</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1501617397871002</v>
+        <v>0.1501617397871001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3590,7 +3602,7 @@
         <v>0.597</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1675052141563634</v>
+        <v>0.1675052141563633</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3598,7 +3610,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.2955974367465236</v>
+        <v>0.2955974367465235</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3728,7 +3740,7 @@
         <v>0.549</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1780851950115632</v>
+        <v>0.1780851950115631</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3866,7 +3878,7 @@
         <v>0.45</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2065581415389017</v>
+        <v>0.2065581415389016</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3912,7 +3924,7 @@
         <v>0.549</v>
       </c>
       <c r="I76" t="n">
-        <v>0.207816695517155</v>
+        <v>0.2078166955171549</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3958,7 +3970,7 @@
         <v>0.541</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2295798823236165</v>
+        <v>0.2295798823236164</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4058,7 +4070,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0.3705551465164699</v>
+        <v>0.3705551465164698</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4142,7 +4154,7 @@
         <v>-0.481</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2665507039576892</v>
+        <v>0.2665507039576891</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4150,7 +4162,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.3998260559365338</v>
+        <v>0.3998260559365337</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4372,7 +4384,7 @@
         <v>0.311</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3309109978983568</v>
+        <v>0.3309109978983567</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4380,7 +4392,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.4671684676212096</v>
+        <v>0.4671684676212095</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4694,7 +4706,7 @@
         <v>0.213</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4660269106413034</v>
+        <v>0.4660269106413033</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4740,7 +4752,7 @@
         <v>0.257</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4798130342744819</v>
+        <v>0.4798130342744818</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5622,7 +5634,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>0.9236131323760675</v>
+        <v>0.9236131323760676</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5668,7 +5680,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0.9236131323760675</v>
+        <v>0.9236131323760676</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5760,7 +5772,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>0.9477445938923319</v>
+        <v>0.947744593892332</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>

--- a/supplementary/Table S3.xlsx
+++ b/supplementary/Table S3.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3 - Co-Occurrence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +26,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,19 +59,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,8 +452,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -471,5542 +514,6272 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>P Value Fisher</t>
+          <t>Unadjusted Fisher P</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Tendency</t>
+          <t>Unadjusted Fisher FDR</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>FDR q Value</t>
+          <t>Unadjusted Significance</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Statistical Significance</t>
+          <t>Permutation Observed/Expected Ratio</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Permutation TMB-Adjusted FDR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Permutation TMB-Adjusted Significance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>1032</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>3.287</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>1.717</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>5.027184316179612e-07</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2" s="3" t="n">
         <v>6.032621179415534e-05</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L2" s="3" t="n">
+        <v>0.8217827206486605</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>1034</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>2.816</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>1.494</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>4.01129536355876e-05</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.0018683444654487</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L3" s="3" t="n">
+        <v>1.481544192346766</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>3.059</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>1.613</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>4.670861163621942e-05</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.0018683444654487</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L4" s="3" t="n">
+        <v>0.6710058377507885</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>1109</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>3.262</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>1.706</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>6.374420318504608e-05</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.0019123260955513</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L5" s="3" t="n">
+        <v>1.186098920649982</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>1064</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>2.801</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>1.486</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>8.778301601467679e-05</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.0021067923843522</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L6" s="3" t="n">
+        <v>1.197604790419162</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>1130</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>3.443</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>1.784</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>0.0001726626864896</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.0031354070264861</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L7" s="3" t="n">
+        <v>0.8581481163648845</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>1049</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>2.594</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>1.375</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>0.0001937643709938</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.0031354070264861</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L8" s="3" t="n">
+        <v>1.498239568507004</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>1108</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>3.022</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>1.596</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>0.000209027135099</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.0031354070264861</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>1134</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>3.335</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>1.738</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>0.0003438979903858</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.0042949018396258</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L10" s="3" t="n">
+        <v>0.6572893387669252</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>1030</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>2.442</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>1.288</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>0.0003579084866354</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.0042949018396258</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L11" s="3" t="n">
+        <v>0.3809233582203261</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>1062</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>2.541</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>1.345</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>0.0005816052790444</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
+      <c r="J12" s="3" t="n">
         <v>0.0059053739093019</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L12" s="3" t="n">
+        <v>1.801477211313277</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>1149</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>3.442</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>1.783</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>0.0005905373909301</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
+      <c r="J13" s="3" t="n">
         <v>0.0059053739093019</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L13" s="3" t="n">
+        <v>2.359882005899705</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>961</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>1.967</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>0.976</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3" t="n">
         <v>0.0010528605418052</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.009718712693586999</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L14" s="3" t="n">
+        <v>1.031793994958949</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>1133</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>3.024</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1.596</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>0.0011552095093773</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
+      <c r="J15" s="3" t="n">
         <v>0.009901795794663</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L15" s="3" t="n">
+        <v>1.209482341557813</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>1051</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>2.378</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>0.0012631065528885</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
+      <c r="J16" s="3" t="n">
         <v>0.0100255812428592</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L16" s="3" t="n">
+        <v>0.9981036031540074</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>1042</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>2.285</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>1.192</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>0.0013367441657145</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.0100255812428592</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L17" s="3" t="n">
+        <v>0.9349726520499276</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>1057</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>2.373</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>1.246</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>0.0014277034969872</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.010077907037557</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L18" s="3" t="n">
+        <v>1.281503630926954</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3" t="n">
         <v>987</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>2.007</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>1.005</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>0.0015282656977182</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.010188437984788</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L19" s="3" t="n">
+        <v>1.022330621723065</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3" t="n">
         <v>1086</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>2.579</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>1.367</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>0.0022978212602316</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.0145125553277785</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L20" s="3" t="n">
+        <v>1.782637114504724</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3" t="n">
         <v>1031</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>2.148</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>1.103</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3" t="n">
         <v>0.0031026423462161</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.0182970691615658</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L21" s="3" t="n">
+        <v>0.465809577044904</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="3" t="n">
         <v>986</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="3" t="n">
         <v>1.895</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="3" t="n">
         <v>0.922</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="3" t="n">
         <v>0.0033486977842632</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
+      <c r="J22" s="3" t="n">
         <v>0.0182970691615658</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L22" s="3" t="n">
+        <v>1.531950747783459</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="3" t="n">
         <v>973</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="3" t="n">
         <v>1.861</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="3" t="n">
         <v>0.896</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="3" t="n">
         <v>0.0033544626796204</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
+      <c r="J23" s="3" t="n">
         <v>0.0182970691615658</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L23" s="3" t="n">
+        <v>1.192520511352795</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="3" t="n">
         <v>1041</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="3" t="n">
         <v>2.149</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="3" t="n">
         <v>1.103</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="3" t="n">
         <v>0.003571594918896</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
+      <c r="J24" s="3" t="n">
         <v>0.0186344082725012</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L24" s="3" t="n">
+        <v>1.549426712116517</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="3" t="n">
         <v>1004</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="3" t="n">
         <v>1.973</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="3" t="n">
         <v>0.0037396075928264</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
+      <c r="J25" s="3" t="n">
         <v>0.0186980379641323</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L25" s="3" t="n">
+        <v>0.8501774745478118</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="3" t="n">
         <v>1017</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="3" t="n">
         <v>1.993</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3" t="n">
         <v>0.995</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="3" t="n">
         <v>0.0041725913516621</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
+      <c r="J26" s="3" t="n">
         <v>0.0200284384879781</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L26" s="3" t="n">
+        <v>1.547029702970297</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="3" t="n">
         <v>2.312</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>1.209</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="3" t="n">
         <v>0.0045336731652681</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
+      <c r="J27" s="3" t="n">
         <v>0.0201536547271551</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L27" s="3" t="n">
+        <v>0.5172235440157236</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="3" t="n">
         <v>2.178</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3" t="n">
         <v>1.123</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="3" t="n">
         <v>0.0045345723136099</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
+      <c r="J28" s="3" t="n">
         <v>0.0201536547271551</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L28" s="3" t="n">
+        <v>0.5835667600373483</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="3" t="n">
         <v>1027</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="3" t="n">
         <v>2.05</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3" t="n">
         <v>1.036</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="3" t="n">
         <v>0.0050301244286348</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
+      <c r="J29" s="3" t="n">
         <v>0.0215576761227208</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L29" s="3" t="n">
+        <v>1.690938682336032</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0.8099190080991902</v>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="3" t="n">
         <v>1061</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="3" t="n">
         <v>2.143</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="3" t="n">
         <v>0.0055757785055431</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
+      <c r="J30" s="3" t="n">
         <v>0.0230721869194888</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L30" s="3" t="n">
+        <v>1.339270767067332</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="3" t="n">
         <v>964</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="3" t="n">
         <v>1.781</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3" t="n">
         <v>0.832</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="3" t="n">
         <v>0.0060025446575148</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
+      <c r="J31" s="3" t="n">
         <v>0.0240101786300594</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L31" s="3" t="n">
+        <v>0.9566631589017508</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="3" t="n">
         <v>1025</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="3" t="n">
         <v>0.955</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="3" t="n">
         <v>0.007891408201843499</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
+      <c r="J32" s="3" t="n">
         <v>0.0305473865877816</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L32" s="3" t="n">
+        <v>1.168770453482936</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="3" t="n">
         <v>1080</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="3" t="n">
         <v>2.277</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3" t="n">
         <v>1.187</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="3" t="n">
         <v>0.0090618454209405</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
+      <c r="J33" s="3" t="n">
         <v>0.0339819203285272</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L33" s="3" t="n">
+        <v>0.855395406526667</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="3" t="n">
         <v>1041</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="3" t="n">
         <v>1.944</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3" t="n">
         <v>0.959</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="3" t="n">
         <v>0.0135551618026791</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
+      <c r="J34" s="3" t="n">
         <v>0.0489194477276675</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L34" s="3" t="n">
+        <v>0.7791600654494455</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="3" t="n">
         <v>1060</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="3" t="n">
         <v>2.105</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3" t="n">
         <v>1.074</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="3" t="n">
         <v>0.0138605101895057</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
+      <c r="J35" s="3" t="n">
         <v>0.0489194477276675</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Significant (FDR &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L35" s="3" t="n">
+        <v>0.3359763472651525</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="3" t="n">
         <v>1035</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" s="3" t="n">
         <v>1.885</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3" t="n">
         <v>0.915</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="3" t="n">
         <v>0.0167317213194176</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
+      <c r="J36" s="3" t="n">
         <v>0.0573659016665747</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L36" s="3" t="n">
+        <v>0.3334222459322485</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="3" t="n">
         <v>1120</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="3" t="n">
         <v>2.254</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3" t="n">
         <v>1.172</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="3" t="n">
         <v>0.0193937193102553</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
+      <c r="J37" s="3" t="n">
         <v>0.0646457310341844</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L37" s="3" t="n">
+        <v>1.332356272067151</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="3" t="n">
         <v>1014</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="3" t="n">
         <v>1.772</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3" t="n">
         <v>0.825</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="3" t="n">
         <v>0.021175204958691</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
+      <c r="J38" s="3" t="n">
         <v>0.06867634040656539</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L38" s="3" t="n">
+        <v>1.166520851560222</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="3" t="n">
         <v>1062</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="3" t="n">
         <v>1.887</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3" t="n">
         <v>0.916</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="3" t="n">
         <v>0.0228451141121332</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
+      <c r="J39" s="3" t="n">
         <v>0.07214246561726299</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L39" s="3" t="n">
+        <v>0.830702774547267</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="3" t="n">
         <v>1132</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="3" t="n">
         <v>2.236</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3" t="n">
         <v>1.161</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="3" t="n">
         <v>0.0239929309808118</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
+      <c r="J40" s="3" t="n">
         <v>0.0738244030178825</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L40" s="3" t="n">
+        <v>1.312852829197847</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="3" t="n">
         <v>1113</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="3" t="n">
         <v>2.069</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3" t="n">
         <v>1.049</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="3" t="n">
         <v>0.026710030798612</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
+      <c r="J41" s="3" t="n">
         <v>0.0801300923958362</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L41" s="3" t="n">
+        <v>2.552322613578356</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="3" t="n">
         <v>1108</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="3" t="n">
         <v>2.097</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3" t="n">
         <v>1.069</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="3" t="n">
         <v>0.0290692377534533</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
+      <c r="J42" s="3" t="n">
         <v>0.0850806958637659</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L42" s="3" t="n">
+        <v>0.9353661958656816</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="3" t="n">
         <v>1105</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="3" t="n">
         <v>2.024</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>1.017</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="3" t="n">
         <v>0.03160070795986</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
+      <c r="J43" s="3" t="n">
         <v>0.09016375027261329</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L43" s="3" t="n">
+        <v>0.6639665360865813</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="3" t="n">
         <v>1140</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="3" t="n">
         <v>2.22</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3" t="n">
         <v>1.151</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="3" t="n">
         <v>0.0323086771810197</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
+      <c r="J44" s="3" t="n">
         <v>0.09016375027261329</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L44" s="3" t="n">
+        <v>1.702417432754511</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="3" t="n">
         <v>991</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="3" t="n">
         <v>1.605</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="3" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="3" t="n">
         <v>0.0350133910189028</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
+      <c r="J45" s="3" t="n">
         <v>0.0954910664151896</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L45" s="3" t="n">
+        <v>0.8338336335134413</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="3" t="n">
         <v>1052</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="3" t="n">
         <v>1.846</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="3" t="n">
         <v>0.885</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="3" t="n">
         <v>0.0397816771903569</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
+      <c r="J46" s="3" t="n">
         <v>0.1060844725076186</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L46" s="3" t="n">
+        <v>0.9262689885142646</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="3" t="n">
         <v>1109</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="3" t="n">
         <v>1.95</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="3" t="n">
         <v>0.963</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="3" t="n">
         <v>0.046179636750885</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
+      <c r="J47" s="3" t="n">
         <v>0.1204686176110044</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L47" s="3" t="n">
+        <v>0.9384384384384384</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="3" t="n">
         <v>967</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="3" t="n">
         <v>1.533</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="3" t="n">
         <v>0.616</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="3" t="n">
         <v>0.0484577591212298</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
+      <c r="J48" s="3" t="n">
         <v>0.1237219381818634</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Nominally Significant (P &lt; 0.05)</t>
         </is>
       </c>
+      <c r="L48" s="3" t="n">
+        <v>1.075596507896671</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="3" t="n">
         <v>1061</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="3" t="n">
         <v>1.751</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="3" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="3" t="n">
         <v>0.0503584837108112</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
+      <c r="J49" s="3" t="n">
         <v>0.1258962092770282</v>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.4679457182966776</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="3" t="n">
         <v>1.572</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="3" t="n">
         <v>0.653</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" s="3" t="n">
         <v>0.055277121952554</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
+      <c r="J50" s="3" t="n">
         <v>0.1353725435572753</v>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>1.133058881293198</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="3" t="n">
         <v>1122</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="3" t="n">
         <v>1.926</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="3" t="n">
         <v>0.946</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="3" t="n">
         <v>0.0571246959112406</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
+      <c r="J51" s="3" t="n">
         <v>0.1370992701869776</v>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>1.86880956830499</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="3" t="n">
         <v>1117</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="3" t="n">
         <v>1.978</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="3" t="n">
         <v>0.984</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="3" t="n">
         <v>0.0598954686809403</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
+      <c r="J52" s="3" t="n">
         <v>0.1383862447503476</v>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>1.332622601279318</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="3" t="n">
         <v>182</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="3" t="n">
         <v>945</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="3" t="n">
         <v>1.478</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="3" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="3" t="n">
         <v>0.0599673727251506</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
+      <c r="J53" s="3" t="n">
         <v>0.1383862447503476</v>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>1.308429557423702</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="3" t="n">
         <v>977</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" s="3" t="n">
         <v>1.505</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="3" t="n">
         <v>0.59</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="3" t="n">
         <v>0.0708504952803036</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
+      <c r="J54" s="3" t="n">
         <v>0.1604162157289894</v>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>1.504150086830482</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0.8099190080991902</v>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="3" t="n">
         <v>1080</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" s="3" t="n">
         <v>1.672</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="3" t="n">
         <v>0.741</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="3" t="n">
         <v>0.083555230424624</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
+      <c r="J55" s="3" t="n">
         <v>0.1825034731560954</v>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="3" t="n">
         <v>1031</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" s="3" t="n">
         <v>1.582</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="3" t="n">
         <v>0.662</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="3" t="n">
         <v>0.0855686913768373</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
+      <c r="J56" s="3" t="n">
         <v>0.1825034731560954</v>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.6629321488945606</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="3" t="n">
         <v>1005</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="3" t="n">
         <v>1.505</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="3" t="n">
         <v>0.59</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" s="3" t="n">
         <v>0.0863989034409669</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
+      <c r="J57" s="3" t="n">
         <v>0.1825034731560954</v>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.8105041335710812</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="3" t="n">
         <v>1032</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="3" t="n">
         <v>1.619</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="3" t="n">
         <v>0.695</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="3" t="n">
         <v>0.08771500970140771</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
+      <c r="J58" s="3" t="n">
         <v>0.1825034731560954</v>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>1.361359181006317</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="3" t="n">
         <v>1094</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="3" t="n">
         <v>1.737</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="3" t="n">
         <v>0.796</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="3" t="n">
         <v>0.08821001202544609</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
+      <c r="J59" s="3" t="n">
         <v>0.1825034731560954</v>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>1.059546514091969</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="3" t="n">
         <v>1002</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" s="3" t="n">
         <v>1.478</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="3" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60" s="3" t="n">
         <v>0.0943019877705014</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
+      <c r="J60" s="3" t="n">
         <v>0.1918006530925453</v>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>1.310100877767588</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="3" t="n">
         <v>1116</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" s="3" t="n">
         <v>1.768</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="3" t="n">
         <v>0.822</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" s="3" t="n">
         <v>0.0985887856512232</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
+      <c r="J61" s="3" t="n">
         <v>0.1971775713024465</v>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="3" t="n">
         <v>1101</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" s="3" t="n">
         <v>1.777</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62" s="3" t="n">
         <v>0.1091284625150077</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
+      <c r="J62" s="3" t="n">
         <v>0.2146789426524742</v>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.7472724555372888</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="3" t="n">
         <v>1045</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="3" t="n">
         <v>0.622</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63" s="3" t="n">
         <v>0.1204271216760866</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
+      <c r="J63" s="3" t="n">
         <v>0.2330847516311354</v>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>1.040474456352097</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="3" t="n">
         <v>1031</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" s="3" t="n">
         <v>1.503</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="3" t="n">
         <v>0.588</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64" s="3" t="n">
         <v>0.1327890434709118</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
+      <c r="J64" s="3" t="n">
         <v>0.2529315113731653</v>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>2.152466367713004</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>0.8099190080991902</v>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="3" t="n">
         <v>1011</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" s="3" t="n">
         <v>1.447</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="3" t="n">
         <v>0.533</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65" s="3" t="n">
         <v>0.1423254556440676</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
+      <c r="J65" s="3" t="n">
         <v>0.2668602293326269</v>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>1.48995768520174</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="3" t="n">
         <v>1055</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" s="3" t="n">
         <v>1.555</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="3" t="n">
         <v>0.637</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66" s="3" t="n">
         <v>0.147834126537775</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
+      <c r="J66" s="3" t="n">
         <v>0.2729245413005077</v>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>1.994747165796735</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>0.9863013698630138</v>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="3" t="n">
         <v>1034</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" s="3" t="n">
         <v>1.448</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="3" t="n">
         <v>0.534</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" s="3" t="n">
         <v>0.1501617397871001</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
+      <c r="J67" s="3" t="n">
         <v>0.2730213450674548</v>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.9314889851427508</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="3" t="n">
         <v>1066</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" s="3" t="n">
         <v>1.599</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="3" t="n">
         <v>0.677</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68" s="3" t="n">
         <v>0.1527786675691465</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
+      <c r="J68" s="3" t="n">
         <v>0.2736334344522027</v>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>1.497174083916607</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="3" t="n">
         <v>1078</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" s="3" t="n">
         <v>1.513</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="3" t="n">
         <v>0.597</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69" s="3" t="n">
         <v>0.1675052141563633</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
+      <c r="J69" s="3" t="n">
         <v>0.2955974367465235</v>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="3" t="n">
         <v>1059</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" s="3" t="n">
         <v>1.537</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70" s="3" t="n">
         <v>0.1732561804311238</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
+      <c r="J70" s="3" t="n">
         <v>0.2976468215200433</v>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>1.572739187418086</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="3" t="n">
         <v>993</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" s="3" t="n">
         <v>1.421</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="3" t="n">
         <v>0.507</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" s="3" t="n">
         <v>0.1736273125533586</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
+      <c r="J71" s="3" t="n">
         <v>0.2976468215200433</v>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>1.490979573579842</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="3" t="n">
         <v>1029</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="3" t="n">
         <v>1.463</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="3" t="n">
         <v>0.549</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="3" t="n">
         <v>0.1780851950115631</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
+      <c r="J72" s="3" t="n">
         <v>0.3009890619913744</v>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>1.081938834391229</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="3" t="n">
         <v>177</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="3" t="n">
         <v>1042</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" s="3" t="n">
         <v>1.472</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="3" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="3" t="n">
         <v>0.1843235733908335</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
+      <c r="J73" s="3" t="n">
         <v>0.3072059556513892</v>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>1.094900500916979</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="3" t="n">
         <v>1038</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" s="3" t="n">
         <v>1.468</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="3" t="n">
         <v>0.553</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="3" t="n">
         <v>0.2062485633573579</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
+      <c r="J74" s="3" t="n">
         <v>0.332506712827448</v>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>1.387475719174914</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="3" t="n">
         <v>992</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" s="3" t="n">
         <v>1.366</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="3" t="n">
         <v>0.2065581415389016</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
+      <c r="J75" s="3" t="n">
         <v>0.332506712827448</v>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.2334485012606219</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>0.8099190080991902</v>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="3" t="n">
         <v>1046</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" s="3" t="n">
         <v>1.464</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="3" t="n">
         <v>0.549</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76" s="3" t="n">
         <v>0.2078166955171549</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
+      <c r="J76" s="3" t="n">
         <v>0.332506712827448</v>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.8787346221441125</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="3" t="n">
         <v>1068</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" s="3" t="n">
         <v>1.455</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="3" t="n">
         <v>0.541</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77" s="3" t="n">
         <v>0.2295798823236164</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
+      <c r="J77" s="3" t="n">
         <v>0.3602704239566293</v>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.5991970759182695</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="3" t="n">
         <v>1004</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" s="3" t="n">
         <v>1.353</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="3" t="n">
         <v>0.436</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78" s="3" t="n">
         <v>0.2311735220388371</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
+      <c r="J78" s="3" t="n">
         <v>0.3602704239566293</v>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>1.794236911041734</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="3" t="n">
         <v>996</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" s="3" t="n">
         <v>1.342</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="3" t="n">
         <v>0.425</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" s="3" t="n">
         <v>0.2408608452357054</v>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
+      <c r="J79" s="3" t="n">
         <v>0.3705551465164698</v>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1.190986613310466</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="3" t="n">
         <v>1049</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" s="3" t="n">
         <v>1.428</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="3" t="n">
         <v>0.514</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80" s="3" t="n">
         <v>0.2462701684771314</v>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
+      <c r="J80" s="3" t="n">
         <v>0.3740812685728578</v>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>1.881733076163146</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="3" t="n">
         <v>962</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" s="3" t="n">
         <v>0.716</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="3" t="n">
         <v>-0.481</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" s="3" t="n">
         <v>0.2665507039576891</v>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
+      <c r="J81" s="3" t="n">
         <v>0.3998260559365337</v>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>1.319348241968468</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="3" t="n">
         <v>1120</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" s="3" t="n">
         <v>1.497</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="3" t="n">
         <v>0.582</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82" s="3" t="n">
         <v>0.2846250502911255</v>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
+      <c r="J82" s="3" t="n">
         <v>0.4216667411720378</v>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>3.391555027980329</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="3" t="n">
         <v>1080</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" s="3" t="n">
         <v>1.424</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83" s="3" t="n">
         <v>0.2900001618358659</v>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
+      <c r="J83" s="3" t="n">
         <v>0.4243904807354135</v>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>1.02981308892436</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="3" t="n">
         <v>1028</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" s="3" t="n">
         <v>1.359</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84" s="3" t="n">
         <v>0.443</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84" s="3" t="n">
         <v>0.2952402353813254</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
+      <c r="J84" s="3" t="n">
         <v>0.4268533523585427</v>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>1.304971943103223</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="3" t="n">
         <v>1106</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85" s="3" t="n">
         <v>1.396</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85" s="3" t="n">
         <v>0.482</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85" s="3" t="n">
         <v>0.3254960294857917</v>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
+      <c r="J85" s="3" t="n">
         <v>0.4649943278368453</v>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.5170898185014737</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="3" t="n">
         <v>980</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="3" t="n">
         <v>1.241</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="3" t="n">
         <v>0.311</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="3" t="n">
         <v>0.3309109978983567</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
+      <c r="J86" s="3" t="n">
         <v>0.4671684676212095</v>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>1.620032863523803</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="3" t="n">
         <v>971</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" s="3" t="n">
         <v>1.254</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87" s="3" t="n">
         <v>0.326</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87" s="3" t="n">
         <v>0.341627478210468</v>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
+      <c r="J87" s="3" t="n">
         <v>0.4766895044797228</v>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>1.412914034273258</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="3" t="n">
         <v>1125</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88" s="3" t="n">
         <v>0.491</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88" s="3" t="n">
         <v>-1.028</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88" s="3" t="n">
         <v>0.3651340594746505</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
+      <c r="J88" s="3" t="n">
         <v>0.5036331854822765</v>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" s="3" t="n">
         <v>1072</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89" s="3" t="n">
         <v>1.295</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89" s="3" t="n">
         <v>0.373</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89" s="3" t="n">
         <v>0.3973489388353819</v>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
+      <c r="J89" s="3" t="n">
         <v>0.5418394620482481</v>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>1.477759716270135</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" s="3" t="n">
         <v>995</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90" s="3" t="n">
         <v>0.322</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90" s="3" t="n">
         <v>0.4047568453789139</v>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
+      <c r="J90" s="3" t="n">
         <v>0.5457395668030299</v>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>2.341646177262616</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>0.993900609939006</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="3" t="n">
         <v>1059</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91" s="3" t="n">
         <v>1.288</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" s="3" t="n">
         <v>0.365</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91" s="3" t="n">
         <v>0.4122642220469305</v>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
+      <c r="J91" s="3" t="n">
         <v>0.5496856293959073</v>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>1.857700167193015</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" s="3" t="n">
         <v>1087</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92" s="3" t="n">
         <v>1.299</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92" s="3" t="n">
         <v>0.378</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92" s="3" t="n">
         <v>0.4612454259619805</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
+      <c r="J92" s="3" t="n">
         <v>0.6078611877930044</v>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>2.005883926183472</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="3" t="n">
         <v>919</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93" s="3" t="n">
         <v>1.159</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93" s="3" t="n">
         <v>0.213</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93" s="3" t="n">
         <v>0.4660269106413033</v>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
+      <c r="J93" s="3" t="n">
         <v>0.6078611877930044</v>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>1.423251180112437</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="3" t="n">
         <v>1026</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" s="3" t="n">
         <v>1.195</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94" s="3" t="n">
         <v>0.257</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94" s="3" t="n">
         <v>0.4798130342744818</v>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
+      <c r="J94" s="3" t="n">
         <v>0.6191135926122346</v>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>1.127141568981064</v>
+      </c>
+      <c r="M94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" s="3" t="n">
         <v>1041</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" s="3" t="n">
         <v>1.242</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95" s="3" t="n">
         <v>0.313</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95" s="3" t="n">
         <v>0.5146257526494943</v>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
+      <c r="J95" s="3" t="n">
         <v>0.6569690459355246</v>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>1.298364061282784</v>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" s="3" t="n">
         <v>983</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96" s="3" t="n">
         <v>1.161</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96" s="3" t="n">
         <v>0.215</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.5355591131204525</v>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
+      <c r="J96" s="3" t="n">
         <v>0.676495721836361</v>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>1.617233237377495</v>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="3" t="n">
         <v>948</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" s="3" t="n">
         <v>1.139</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" s="3" t="n">
         <v>0.188</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.5692386282898207</v>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
+      <c r="J97" s="3" t="n">
         <v>0.7095815788161954</v>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>1.870557426112982</v>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>NR1D2</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="3" t="n">
         <v>994</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98" s="3" t="n">
         <v>1.166</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H98" s="3" t="n">
         <v>0.221</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I98" s="3" t="n">
         <v>0.5785831627347702</v>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
+      <c r="J98" s="3" t="n">
         <v>0.7095815788161954</v>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>2.086375964948884</v>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="3" t="n">
         <v>1016</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99" s="3" t="n">
         <v>1.175</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H99" s="3" t="n">
         <v>0.233</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I99" s="3" t="n">
         <v>0.5805340334375086</v>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
+      <c r="J99" s="3" t="n">
         <v>0.7095815788161954</v>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>0.9856748587199368</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="3" t="n">
         <v>1082</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" s="3" t="n">
         <v>0.751</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="3" t="n">
         <v>-0.413</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="3" t="n">
         <v>0.5854048025233612</v>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
+      <c r="J100" s="3" t="n">
         <v>0.7095815788161954</v>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.758322590429969</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>PER1</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" s="3" t="n">
         <v>919</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101" s="3" t="n">
         <v>0.864</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H101" s="3" t="n">
         <v>-0.212</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I101" s="3" t="n">
         <v>0.5954987779044788</v>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
+      <c r="J101" s="3" t="n">
         <v>0.7145985334853745</v>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.8097165991902834</v>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102" s="3" t="n">
         <v>1061</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102" s="3" t="n">
         <v>1.148</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H102" s="3" t="n">
         <v>0.199</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I102" s="3" t="n">
         <v>0.6153232769159347</v>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
+      <c r="J102" s="3" t="n">
         <v>0.7310771606921996</v>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.8613264427217915</v>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>PER3</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="3" t="n">
         <v>1033</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103" s="3" t="n">
         <v>1.177</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H103" s="3" t="n">
         <v>0.236</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I103" s="3" t="n">
         <v>0.631290754451638</v>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
+      <c r="J103" s="3" t="n">
         <v>0.7414842951266619</v>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>0.3808363165511463</v>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" s="3" t="n">
         <v>1014</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104" s="3" t="n">
         <v>1.135</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H104" s="3" t="n">
         <v>0.183</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I104" s="3" t="n">
         <v>0.6364406866503849</v>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
+      <c r="J104" s="3" t="n">
         <v>0.7414842951266619</v>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>0.7546030787805614</v>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H105" s="3" t="n">
         <v>-0.27</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I105" s="3" t="n">
         <v>0.6604536868005748</v>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
+      <c r="J105" s="3" t="n">
         <v>0.7615255795350891</v>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>2.26534773087669</v>
+      </c>
+      <c r="M105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>PER2</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="3" t="n">
         <v>187</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" s="3" t="n">
         <v>930</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106" s="3" t="n">
         <v>1.098</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106" s="3" t="n">
         <v>0.134</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I106" s="3" t="n">
         <v>0.666334882093203</v>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
+      <c r="J106" s="3" t="n">
         <v>0.7615255795350891</v>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>1.170275014628438</v>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="3" t="n">
         <v>995</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G107" s="3" t="n">
         <v>1.114</v>
       </c>
-      <c r="H107" t="n">
+      <c r="H107" s="3" t="n">
         <v>0.155</v>
       </c>
-      <c r="I107" t="n">
+      <c r="I107" s="3" t="n">
         <v>0.6750613247453099</v>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
+      <c r="J107" s="3" t="n">
         <v>0.7642203676361998</v>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>0.5850690381465012</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" s="3" t="n">
         <v>1091</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108" s="3" t="n">
         <v>1.106</v>
       </c>
-      <c r="H108" t="n">
+      <c r="H108" s="3" t="n">
         <v>0.145</v>
       </c>
-      <c r="I108" t="n">
+      <c r="I108" s="3" t="n">
         <v>0.7073938907752036</v>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
+      <c r="J108" s="3" t="n">
         <v>0.7933389429254619</v>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" s="3" t="n">
         <v>1066</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109" s="3" t="n">
         <v>1.123</v>
       </c>
-      <c r="H109" t="n">
+      <c r="H109" s="3" t="n">
         <v>0.168</v>
       </c>
-      <c r="I109" t="n">
+      <c r="I109" s="3" t="n">
         <v>0.7271432920227641</v>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
+      <c r="J109" s="3" t="n">
         <v>0.8079369911364046</v>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>1.212268153715602</v>
+      </c>
+      <c r="M109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="3" t="n">
         <v>1007</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110" s="3" t="n">
         <v>1.089</v>
       </c>
-      <c r="H110" t="n">
+      <c r="H110" s="3" t="n">
         <v>0.123</v>
       </c>
-      <c r="I110" t="n">
+      <c r="I110" s="3" t="n">
         <v>0.762574488118323</v>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
+      <c r="J110" s="3" t="n">
         <v>0.8395315465522822</v>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>1.032951141411011</v>
+      </c>
+      <c r="M110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111" s="3" t="n">
         <v>1029</v>
       </c>
-      <c r="G111" t="n">
+      <c r="G111" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="H111" t="n">
+      <c r="H111" s="3" t="n">
         <v>0.097</v>
       </c>
-      <c r="I111" t="n">
+      <c r="I111" s="3" t="n">
         <v>0.7741726296859321</v>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
+      <c r="J111" s="3" t="n">
         <v>0.8445519596573805</v>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>0.5277601857715853</v>
+      </c>
+      <c r="M111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>CSNK1D</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" s="3" t="n">
         <v>1098</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G112" s="3" t="n">
         <v>1.084</v>
       </c>
-      <c r="H112" t="n">
+      <c r="H112" s="3" t="n">
         <v>0.116</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I112" s="3" t="n">
         <v>0.8419895747276529</v>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
+      <c r="J112" s="3" t="n">
         <v>0.9102589997055708</v>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="n">
+        <v>0.6639665360865813</v>
+      </c>
+      <c r="M112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>CRY1</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113" s="3" t="n">
         <v>1073</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G113" s="3" t="n">
         <v>0.877</v>
       </c>
-      <c r="H113" t="n">
+      <c r="H113" s="3" t="n">
         <v>-0.189</v>
       </c>
-      <c r="I113" t="n">
+      <c r="I113" s="3" t="n">
         <v>0.8627723617164068</v>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
+      <c r="J113" s="3" t="n">
         <v>0.9236131323760676</v>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="n">
+        <v>0.5899705014749262</v>
+      </c>
+      <c r="M113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>CSNK1E</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NPAS2</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="3" t="n">
         <v>1.056</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="3" t="n">
         <v>0.078</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="3" t="n">
         <v>0.8697356996541301</v>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
+      <c r="J114" s="3" t="n">
         <v>0.9236131323760676</v>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="n">
+        <v>1.492370257060777</v>
+      </c>
+      <c r="M114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="3" t="n">
         <v>1047</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="H115" t="n">
+      <c r="H115" s="3" t="n">
         <v>-0.136</v>
       </c>
-      <c r="I115" t="n">
+      <c r="I115" s="3" t="n">
         <v>0.877821390895281</v>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
+      <c r="J115" s="3" t="n">
         <v>0.9240225167318746</v>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>1.756337450968913</v>
+      </c>
+      <c r="M115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116" s="3" t="n">
         <v>1.024</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H116" s="3" t="n">
         <v>0.034</v>
       </c>
-      <c r="I116" t="n">
+      <c r="I116" s="3" t="n">
         <v>0.9082552358134848</v>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K116" t="n">
+      <c r="J116" s="3" t="n">
         <v>0.947744593892332</v>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>0.5222750300308142</v>
+      </c>
+      <c r="M116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>ARNTL</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="3" t="n">
         <v>1112</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117" s="3" t="n">
         <v>0.875</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H117" s="3" t="n">
         <v>-0.192</v>
       </c>
-      <c r="I117" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K117" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="I117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>RORB</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="3" t="n">
         <v>1069</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118" s="3" t="n">
         <v>0.916</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H118" s="3" t="n">
         <v>-0.127</v>
       </c>
-      <c r="I118" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K118" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="I118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>NR1D1</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" s="3" t="n">
         <v>1119</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G119" s="3" t="n">
         <v>0.948</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H119" s="3" t="n">
         <v>-0.077</v>
       </c>
-      <c r="I119" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Mutual Exclusivity</t>
-        </is>
-      </c>
-      <c r="K119" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="I119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>CRY2</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>RORC</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="3" t="n">
         <v>1076</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" s="3" t="n">
         <v>1.019</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" s="3" t="n">
         <v>0.027</v>
       </c>
-      <c r="I120" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="I120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>1.15700566932778</v>
+      </c>
+      <c r="M120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>RORA</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>TIMELESS</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="3" t="n">
         <v>968</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H121" s="3" t="n">
         <v>0.015</v>
       </c>
-      <c r="I121" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Co-occurrence</t>
-        </is>
-      </c>
-      <c r="K121" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Not Significant</t>
+      <c r="I121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>1.16767865483419</v>
+      </c>
+      <c r="M121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Not Significant (FDR &gt;= 0.05)</t>
         </is>
       </c>
     </row>
